--- a/slots/resources/sample/golbal.xlsx
+++ b/slots/resources/sample/golbal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59128FA-BAFF-4357-8650-9E729F21E1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333F60A5-7F00-46CA-AC5F-68F7B6F0AFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,37 +76,42 @@
     <t>sweet win</t>
   </si>
   <si>
-    <t>500,1000</t>
-  </si>
-  <si>
     <t>slot中奖倍数大于押注倍数后触发大奖表现。此配置下限 &gt;= 【中奖金额 ÷ baseRoom表_单线押分 ÷ baseRoom表_押分系数】 &gt; 此配置范围时，展示表现</t>
   </si>
   <si>
     <t>big win</t>
   </si>
   <si>
-    <t>1000,2000</t>
-  </si>
-  <si>
     <t>mega win</t>
   </si>
   <si>
-    <t>2000,3000</t>
-  </si>
-  <si>
     <t>epic win</t>
   </si>
   <si>
-    <t>3000,5000</t>
-  </si>
-  <si>
     <t>legendary win</t>
   </si>
   <si>
-    <t>5000,9999999</t>
-  </si>
-  <si>
     <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,50</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,9999999</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -195,14 +200,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,8 +521,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>28</v>
+      <c r="A3" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -604,11 +609,11 @@
       <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
         <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -616,13 +621,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -630,13 +635,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -644,13 +649,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,13 +663,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
